--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484691_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484691_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>15.9463</v>
+        <v>13.828</v>
       </c>
       <c r="E2" t="n">
-        <v>12.4848</v>
+        <v>10.4656</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4615</v>
+        <v>3.3624</v>
       </c>
       <c r="G2" t="n">
         <v>8.617000000000001</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7454</v>
+        <v>1.6271</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2406</v>
+        <v>1.2214</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5048</v>
+        <v>0.4057</v>
       </c>
       <c r="V2" t="n">
         <v>1.5681</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.257</v>
+        <v>9.5425</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8249</v>
+        <v>5.2095</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4321</v>
+        <v>4.333</v>
       </c>
       <c r="G3" t="n">
         <v>8.1775</v>
@@ -688,13 +688,13 @@
         <v>2.7489</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9799</v>
+        <v>1.2654</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0355</v>
+        <v>0.4201</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9445</v>
+        <v>0.8454</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6335</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.8041</v>
+        <v>7.3285</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3094</v>
+        <v>5.9825</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4947</v>
+        <v>1.346</v>
       </c>
       <c r="G4" t="n">
         <v>4.7576</v>
@@ -766,13 +766,13 @@
         <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4522</v>
+        <v>0.9766</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3673</v>
+        <v>0.3058</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8194</v>
+        <v>0.6708</v>
       </c>
       <c r="V4" t="n">
         <v>0.3115</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.682</v>
+        <v>7.1332</v>
       </c>
       <c r="E5" t="n">
-        <v>4.927</v>
+        <v>6.0809</v>
       </c>
       <c r="F5" t="n">
-        <v>0.755</v>
+        <v>1.0523</v>
       </c>
       <c r="G5" t="n">
         <v>3.11</v>
@@ -844,13 +844,13 @@
         <v>1.4661</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2784</v>
+        <v>1.1727</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.221</v>
+        <v>0.9329</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0575</v>
+        <v>0.2398</v>
       </c>
       <c r="V5" t="n">
         <v>4.1333</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. MASIP CANTERO</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.7711</v>
+        <v>2.7643</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6551</v>
+        <v>0.6533</v>
       </c>
       <c r="F6" t="n">
-        <v>0.116</v>
+        <v>2.111</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2383</v>
+        <v>4.5313</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7225</v>
+        <v>3.4061</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4842</v>
+        <v>1.1252</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1499</v>
+        <v>3.4769</v>
       </c>
       <c r="K6" t="n">
-        <v>4.6659</v>
+        <v>3.217</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.516</v>
+        <v>0.2599</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9116</v>
+        <v>1.0545</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9434</v>
+        <v>0.1891</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0318</v>
+        <v>0.8653</v>
       </c>
       <c r="P6" t="n">
         <v>-1.0995</v>
@@ -922,28 +922,28 @@
         <v>1.8326</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2659</v>
+        <v>0.6099</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4819</v>
+        <v>0.4201</v>
       </c>
       <c r="U6" t="n">
-        <v>0.784</v>
+        <v>0.1898</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6335</v>
+        <v>-1.2774</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9554</v>
+        <v>-0.3115</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5889</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GADEA HIERRO</t>
+          <t>D. MASIP CANTERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.438</v>
+        <v>2.6055</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9283</v>
+        <v>2.8859</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5097</v>
+        <v>-0.2804</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.3447</v>
+        <v>3.2383</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3798</v>
+        <v>3.7225</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9649</v>
+        <v>-0.4842</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.7797</v>
+        <v>4.1499</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6226</v>
+        <v>4.6659</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.157</v>
+        <v>-0.516</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.9116</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7572</v>
+        <v>-0.9434</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1922</v>
+        <v>0.0318</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2828</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.9321</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2828</v>
+        <v>1.8326</v>
       </c>
       <c r="S7" t="n">
-        <v>1.267</v>
+        <v>1.1003</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4751</v>
+        <v>0.7127</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7919</v>
+        <v>0.3876</v>
       </c>
       <c r="V7" t="n">
-        <v>2.2328</v>
+        <v>-0.6335</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2328</v>
+        <v>0.9554</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>A. GADEA HIERRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0577</v>
+        <v>2.3578</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2687</v>
+        <v>1.1206</v>
       </c>
       <c r="F8" t="n">
-        <v>1.789</v>
+        <v>1.2372</v>
       </c>
       <c r="G8" t="n">
-        <v>4.5313</v>
+        <v>-2.3447</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4061</v>
+        <v>-1.3798</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1252</v>
+        <v>-0.9649</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4769</v>
+        <v>-1.7797</v>
       </c>
       <c r="K8" t="n">
-        <v>3.217</v>
+        <v>-0.6226</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2599</v>
+        <v>-1.157</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0545</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1891</v>
+        <v>-0.7572</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8653</v>
+        <v>0.1922</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.0995</v>
+        <v>1.2828</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9321</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8326</v>
+        <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0968</v>
+        <v>1.1868</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0355</v>
+        <v>0.6674</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1322</v>
+        <v>0.5194</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2774</v>
+        <v>2.2328</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3115</v>
+        <v>2.2328</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>A. MONRABAL ROMEU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1103</v>
+        <v>0.1203</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6961000000000001</v>
+        <v>0.3962</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8063</v>
+        <v>-0.2759</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.641</v>
+        <v>0.0373</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.641</v>
+        <v>-1.5301</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1.5674</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.641</v>
+        <v>1.3411</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.641</v>
+        <v>-0.0341</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.3753</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-1.3038</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.1922</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1833</v>
+        <v>0.3665</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1833</v>
+        <v>1.4661</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0551</v>
+        <v>-0.2836</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0551</v>
+        <v>0.1546</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0.4382</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MONRABAL ROMEU</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0153</v>
+        <v>0.1103</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5885</v>
+        <v>-0.6961000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5732</v>
+        <v>0.8063</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0373</v>
+        <v>-0.641</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5301</v>
+        <v>-0.641</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5674</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3411</v>
+        <v>-0.641</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0341</v>
+        <v>-0.641</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3753</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3038</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1922</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4661</v>
+        <v>0.1833</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3885</v>
+        <v>-0.0551</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3469</v>
+        <v>-0.0551</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7355</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. GOMEZ CARBONELL</t>
+          <t>I. BOU MINARRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7621</v>
+        <v>-0.4917</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2041</v>
+        <v>-0.2467</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9661999999999999</v>
+        <v>-0.245</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3928</v>
+        <v>0.2504</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6686</v>
+        <v>-1.7755</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2758</v>
+        <v>2.0258</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2683</v>
+        <v>0.8626</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2167</v>
+        <v>-0.5543</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0515</v>
+        <v>1.4169</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6611</v>
+        <v>-0.6122</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8854</v>
+        <v>-1.2211</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2243</v>
+        <v>0.6089</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1833</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R12" t="n">
-        <v>0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="S12" t="n">
-        <v>0.759</v>
+        <v>-0.3756</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5302</v>
+        <v>-0.1931</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2288</v>
+        <v>-0.1825</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.945</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. BOU MINARRO</t>
+          <t>J. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8822</v>
+        <v>-0.8612</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4391</v>
+        <v>0.2041</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4431</v>
+        <v>-1.0653</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2504</v>
+        <v>-0.3928</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7755</v>
+        <v>-0.6686</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0258</v>
+        <v>0.2758</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8626</v>
+        <v>0.2683</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5543</v>
+        <v>0.2167</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4169</v>
+        <v>0.0515</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6122</v>
+        <v>-0.6611</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2211</v>
+        <v>-0.8854</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6089</v>
+        <v>0.2243</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3665</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7661</v>
+        <v>0.6599</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3854</v>
+        <v>0.5302</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3807</v>
+        <v>0.1297</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.945</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="14">
@@ -1504,13 +1504,13 @@
         <v>44.76260000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>32.3807</v>
+        <v>32.3809</v>
       </c>
       <c r="F14" t="n">
-        <v>12.3818</v>
+        <v>12.3816</v>
       </c>
       <c r="G14" t="n">
-        <v>29.66599999999999</v>
+        <v>29.666</v>
       </c>
       <c r="H14" t="n">
         <v>12.5158</v>
@@ -1546,10 +1546,10 @@
         <v>15.5771</v>
       </c>
       <c r="S14" t="n">
-        <v>7.884500000000001</v>
+        <v>7.8844</v>
       </c>
       <c r="T14" t="n">
-        <v>5.1169</v>
+        <v>5.116999999999999</v>
       </c>
       <c r="U14" t="n">
         <v>2.7675</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9042</v>
+        <v>0.2732</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0908</v>
+        <v>1.8023</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1866</v>
+        <v>-1.5291</v>
       </c>
       <c r="G15" t="n">
         <v>0.2087</v>
@@ -1624,13 +1624,13 @@
         <v>0.9163</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2392</v>
+        <v>-0.8701</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0196</v>
+        <v>-0.3081</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2196</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>0.9346</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9919</v>
+        <v>-0.7719</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8763</v>
+        <v>-0.7802</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1155</v>
+        <v>0.0083</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7887</v>
@@ -1702,13 +1702,13 @@
         <v>0.5498</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.431</v>
+        <v>-0.211</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3854</v>
+        <v>-0.2892</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0456</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3219</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2558</v>
+        <v>-1.4743</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6027</v>
+        <v>0.9296</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.8585</v>
+        <v>-2.404</v>
       </c>
       <c r="G17" t="n">
         <v>-1.8042</v>
@@ -1780,13 +1780,13 @@
         <v>1.8326</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6065</v>
+        <v>0.388</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.1671</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2336</v>
+        <v>0.221</v>
       </c>
       <c r="V17" t="n">
         <v>-0.0581</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.9617</v>
+        <v>-2.478</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6775</v>
+        <v>-1.2929</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2842</v>
+        <v>-1.1851</v>
       </c>
       <c r="G18" t="n">
         <v>-2.9643</v>
@@ -1858,13 +1858,13 @@
         <v>1.4661</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8691</v>
+        <v>-0.3854</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5505</v>
+        <v>-0.1659</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3186</v>
+        <v>-0.2195</v>
       </c>
       <c r="V18" t="n">
         <v>0.3219</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0578</v>
+        <v>-2.8408</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.217</v>
+        <v>-2.0247</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8408</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>-1.195</v>
@@ -1936,13 +1936,13 @@
         <v>0.1833</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4963</v>
+        <v>-0.2792</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1471</v>
+        <v>0.0453</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3493</v>
+        <v>-0.3245</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6335</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3779</v>
+        <v>-2.8898</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7676</v>
+        <v>-1.383</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6103</v>
+        <v>-1.5068</v>
       </c>
       <c r="G20" t="n">
         <v>-2.6879</v>
@@ -2014,13 +2014,13 @@
         <v>0.733</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0429</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9359</v>
+        <v>-0.5513</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.107</v>
+        <v>-0.0036</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3801</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0281</v>
+        <v>-3.2807</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3576</v>
+        <v>0.3155</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.6705</v>
+        <v>-3.5961</v>
       </c>
       <c r="G21" t="n">
         <v>-4.5138</v>
@@ -2092,13 +2092,13 @@
         <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2521</v>
+        <v>-0.5047</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8077</v>
+        <v>-0.1346</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4444</v>
+        <v>-0.3701</v>
       </c>
       <c r="V21" t="n">
         <v>1.188</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. FOS CERVERA</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8958</v>
+        <v>-5.0916</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2026</v>
+        <v>-0.6814</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.6932</v>
+        <v>-4.4102</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.2921</v>
+        <v>-2.7458</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.9711</v>
+        <v>-1.7233</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.321</v>
+        <v>-1.0225</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7721</v>
+        <v>0.5867</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2144</v>
+        <v>0.5511</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5577</v>
+        <v>0.0356</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.5201</v>
+        <v>-3.3324</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.7567</v>
+        <v>-2.2744</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.7633</v>
+        <v>-1.0581</v>
       </c>
       <c r="P22" t="n">
-        <v>2.0158</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0158</v>
+        <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>1.9309</v>
+        <v>-1.8693</v>
       </c>
       <c r="T22" t="n">
-        <v>1.1509</v>
+        <v>-0.7025</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7801</v>
+        <v>-1.1669</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.5504</v>
+        <v>0.6231</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.5814</v>
+        <v>1.267</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.969</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. CORNEJO GONZALEZ</t>
+          <t>L. BARCOS PERALTA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6415</v>
+        <v>-5.3094</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0131</v>
+        <v>-1.6018</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.6285</v>
+        <v>-3.7076</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9492</v>
+        <v>-1.7858</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0867</v>
+        <v>-0.2024</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.0359</v>
+        <v>-1.5833</v>
       </c>
       <c r="J23" t="n">
-        <v>2.3142</v>
+        <v>-0.4102</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9136</v>
+        <v>0.8203</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5994</v>
+        <v>-1.2305</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.2634</v>
+        <v>-1.3756</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.8269</v>
+        <v>-1.0228</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.4365</v>
+        <v>-0.3528</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5814</v>
+        <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8326</v>
+        <v>0.9163</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4366</v>
+        <v>-1.6127</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2542</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1824</v>
+        <v>-1.0155</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3801</v>
+        <v>-1.9109</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3801</v>
+        <v>-2.2328</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. BARCOS PERALTA</t>
+          <t>M. CORNEJO GONZALEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6503</v>
+        <v>-5.7129</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4095</v>
+        <v>-2.1092</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.2408</v>
+        <v>-3.6037</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.7858</v>
+        <v>-2.9492</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2024</v>
+        <v>0.0867</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5833</v>
+        <v>-3.0359</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4102</v>
+        <v>2.3142</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8203</v>
+        <v>2.9136</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2305</v>
+        <v>-0.5994</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3756</v>
+        <v>-5.2634</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0228</v>
+        <v>-2.8269</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3528</v>
+        <v>-2.4365</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9163</v>
+        <v>-4.5814</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9163</v>
+        <v>1.8326</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9537</v>
+        <v>0.3652</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.405</v>
+        <v>0.158</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.5487</v>
+        <v>0.2072</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.9109</v>
+        <v>-0.3801</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.2328</v>
+        <v>-0.3801</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>B. FOS CERVERA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.9876</v>
+        <v>-6.2917</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.9699</v>
+        <v>-2.2603</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.0177</v>
+        <v>-4.0313</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.7458</v>
+        <v>-6.2921</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7233</v>
+        <v>-3.9711</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0225</v>
+        <v>-2.321</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5867</v>
+        <v>-1.7721</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5511</v>
+        <v>-1.2144</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0356</v>
+        <v>-0.5577</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.3324</v>
+        <v>-4.5201</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.2744</v>
+        <v>-2.7567</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0581</v>
+        <v>-1.7633</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.0995</v>
+        <v>2.0158</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.733</v>
+        <v>2.0158</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.7654</v>
+        <v>0.5351</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9909</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.7744</v>
+        <v>0.4419</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6231</v>
+        <v>-2.5504</v>
       </c>
       <c r="W25" t="n">
-        <v>1.267</v>
+        <v>-0.5814</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6439</v>
+        <v>-1.969</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.8182</v>
+        <v>-6.9717</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.5841</v>
+        <v>-3.2956</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.2341</v>
+        <v>-3.6761</v>
       </c>
       <c r="G26" t="n">
         <v>-2.1479</v>
@@ -2482,13 +2482,13 @@
         <v>1.0995</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.809</v>
+        <v>-0.9625</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.4823</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.0382</v>
+        <v>-0.4802</v>
       </c>
       <c r="V26" t="n">
         <v>-2.212</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-44.7624</v>
+        <v>-42.8396</v>
       </c>
       <c r="E27" t="n">
         <v>-12.3817</v>
       </c>
       <c r="F27" t="n">
-        <v>-32.3807</v>
+        <v>-30.4577</v>
       </c>
       <c r="G27" t="n">
         <v>-29.666</v>
@@ -2539,7 +2539,7 @@
         <v>6.732400000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>-5.287400000000001</v>
+        <v>-5.2874</v>
       </c>
       <c r="M27" t="n">
         <v>-31.1109</v>
@@ -2560,19 +2560,19 @@
         <v>13.7444</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.8847</v>
+        <v>-5.961500000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.7675</v>
+        <v>-2.7676</v>
       </c>
       <c r="U27" t="n">
-        <v>-5.116899999999999</v>
+        <v>-3.194</v>
       </c>
       <c r="V27" t="n">
         <v>-5.3794</v>
       </c>
       <c r="W27" t="n">
-        <v>4.517599999999999</v>
+        <v>4.5176</v>
       </c>
       <c r="X27" t="n">
         <v>-9.8971</v>
